--- a/docs/dealer-programme/DEALER_PROGRAMME_TRACKER_2026-10-29.xlsx
+++ b/docs/dealer-programme/DEALER_PROGRAMME_TRACKER_2026-10-29.xlsx
@@ -71,7 +71,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>Steps 1–10 released 28 Oct (flags off); all-India not released yet</t>
+    <t>Released (flags off): steps 1–10 on 28 Oct; all-India + verification fixes on 29 Oct (release 3, 88d288b)</t>
   </si>
   <si>
     <t>FEE-SLABS</t>
